--- a/demo-knowledge-files/demo-quality-standards.xlsx
+++ b/demo-knowledge-files/demo-quality-standards.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="52">
   <si>
     <t>质量标准编号</t>
   </si>
@@ -134,6 +134,39 @@
   </si>
   <si>
     <t>孔位,导通,全检</t>
+  </si>
+  <si>
+    <t>QLT-HV-SEAL-LOOK</t>
+  </si>
+  <si>
+    <t>防水栓装配外观标准</t>
+  </si>
+  <si>
+    <t>防水栓深度与方向</t>
+  </si>
+  <si>
+    <t>端面齐平，无反装、漏装</t>
+  </si>
+  <si>
+    <t>深度差不超过 0.3 mm</t>
+  </si>
+  <si>
+    <t>首件拍照，过程目视抽检</t>
+  </si>
+  <si>
+    <t>每 30 件抽检 5 件</t>
+  </si>
+  <si>
+    <t>major</t>
+  </si>
+  <si>
+    <t>pending_review</t>
+  </si>
+  <si>
+    <t>防水栓,外观,抽检</t>
+  </si>
+  <si>
+    <t>V2.4 演示用待确认质量标准</t>
   </si>
 </sst>
 </file>
@@ -520,7 +553,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P3"/>
+  <dimension ref="A1:P4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="18" customWidth="1"/>
@@ -677,6 +710,56 @@
         <v>31</v>
       </c>
     </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H4" t="s">
+        <v>43</v>
+      </c>
+      <c r="I4" t="s">
+        <v>44</v>
+      </c>
+      <c r="J4" t="s">
+        <v>45</v>
+      </c>
+      <c r="K4" t="s">
+        <v>46</v>
+      </c>
+      <c r="L4" t="s">
+        <v>47</v>
+      </c>
+      <c r="M4" t="s">
+        <v>48</v>
+      </c>
+      <c r="N4" t="s">
+        <v>49</v>
+      </c>
+      <c r="O4" t="s">
+        <v>50</v>
+      </c>
+      <c r="P4" t="s">
+        <v>51</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
